--- a/artfynd/A 44658-2024 artfynd.xlsx
+++ b/artfynd/A 44658-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1411,6 +1411,129 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>71167242</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Herrgården, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>425662</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6623665</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsbacka</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-05-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-05-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mats Rönngren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mats Rönngren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44658-2024 artfynd.xlsx
+++ b/artfynd/A 44658-2024 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>71167242</v>
       </c>
       <c r="B8" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 44658-2024 artfynd.xlsx
+++ b/artfynd/A 44658-2024 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>71167242</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57488</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
